--- a/Temp/AASTOCKS_Export_2025-7-13.xlsx
+++ b/Temp/AASTOCKS_Export_2025-7-13.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>stockcode</t>
   </si>
@@ -58,102 +58,6 @@
   <si>
     <t>香港交易所</t>
   </si>
-  <si>
-    <t>01299.HK</t>
-  </si>
-  <si>
-    <t>友邦保險</t>
-  </si>
-  <si>
-    <t>00001.HK</t>
-  </si>
-  <si>
-    <t>長和</t>
-  </si>
-  <si>
-    <t>00002.HK</t>
-  </si>
-  <si>
-    <t>中電控股</t>
-  </si>
-  <si>
-    <t>00003.HK</t>
-  </si>
-  <si>
-    <t>香港中華煤氣</t>
-  </si>
-  <si>
-    <t>00066.HK</t>
-  </si>
-  <si>
-    <t>港鐵公司</t>
-  </si>
-  <si>
-    <t>00016.HK</t>
-  </si>
-  <si>
-    <t>新鴻基地產</t>
-  </si>
-  <si>
-    <t>00027.HK</t>
-  </si>
-  <si>
-    <t>銀河娛樂</t>
-  </si>
-  <si>
-    <t>02318.HK</t>
-  </si>
-  <si>
-    <t>中國平安</t>
-  </si>
-  <si>
-    <t>03988.HK</t>
-  </si>
-  <si>
-    <t>中國銀行</t>
-  </si>
-  <si>
-    <t>01398.HK</t>
-  </si>
-  <si>
-    <t>工商銀行</t>
-  </si>
-  <si>
-    <t>00939.HK</t>
-  </si>
-  <si>
-    <t>建設銀行</t>
-  </si>
-  <si>
-    <t>00883.HK</t>
-  </si>
-  <si>
-    <t>中國海洋石油</t>
-  </si>
-  <si>
-    <t>01024.HK</t>
-  </si>
-  <si>
-    <t>快手</t>
-  </si>
-  <si>
-    <t>09988.HK</t>
-  </si>
-  <si>
-    <t>阿里巴巴</t>
-  </si>
-  <si>
-    <t>09618.HK</t>
-  </si>
-  <si>
-    <t>京東集團</t>
-  </si>
-  <si>
-    <t>01810.HK</t>
-  </si>
-  <si>
-    <t>小米集團</t>
-  </si>
 </sst>
 </file>
 
@@ -165,14 +69,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_(&quot;HK$&quot;* #,##0.00_);_(&quot;HK$&quot;* \(#,##0.00\);_(&quot;HK$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,148 +525,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1121,8 +1018,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="4" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1164,134 +1061,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
